--- a/public/templates/examples/A-120-EndpointSecuritySoftwareInventory-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-120-EndpointSecuritySoftwareInventory-EXAMPLE-L.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -195,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -260,6 +265,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,7 +753,7 @@
     <row r="10" ht="27.75" customHeight="1">
       <c r="A10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="50.5" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>ID</t>
@@ -797,7 +805,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>ESS-01</t>
@@ -838,15 +846,11 @@
           <t>IT Team</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
+      <c r="I12" s="26">
+        <v>46048</v>
+      </c>
+      <c r="J12" s="26">
+        <v>46229</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
@@ -890,15 +894,11 @@
           <t>IT Team</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
+      <c r="I13" s="26">
+        <v>46048</v>
+      </c>
+      <c r="J13" s="26">
+        <v>46229</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
@@ -942,15 +942,11 @@
           <t>IT Team</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
+      <c r="I14" s="26">
+        <v>46048</v>
+      </c>
+      <c r="J14" s="26">
+        <v>46229</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
@@ -994,15 +990,11 @@
           <t>IT Team</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
+      <c r="I15" s="26">
+        <v>46048</v>
+      </c>
+      <c r="J15" s="26">
+        <v>46229</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
@@ -1046,15 +1038,11 @@
           <t>IT Team</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
+      <c r="I16" s="26">
+        <v>46048</v>
+      </c>
+      <c r="J16" s="26">
+        <v>46229</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
@@ -1098,15 +1086,11 @@
           <t>IT Team</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
+      <c r="I17" s="26">
+        <v>46048</v>
+      </c>
+      <c r="J17" s="26">
+        <v>46145</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
@@ -1161,7 +1145,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Summary (as of 2026-05-04)</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1158,6 @@
       <c r="B24" s="25" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1186,7 +1169,6 @@
       <c r="B25" s="25" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(C12:C21,"Critical")</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1198,7 +1180,6 @@
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="13">
         <f>COUNTIF(G12:G21,"Meets")</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -1210,7 +1191,6 @@
       <c r="B27" s="25" t="n"/>
       <c r="C27" s="13">
         <f>COUNTIF(G12:G21,"Partial")+COUNTIF(G12:G21,"None")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1222,7 +1202,6 @@
       <c r="B28" s="25" t="n"/>
       <c r="C28" s="13">
         <f>COUNTIFS(C12:C21,"Critical",G12:G21,"Partial")+COUNTIFS(C12:C21,"Critical",G12:G21,"None")</f>
-        <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -1233,8 +1212,7 @@
       </c>
       <c r="B29" s="25" t="n"/>
       <c r="C29" s="13">
-        <f>COUNTIF(J12:J21,"&lt;"&amp;TODAY())</f>
-        <v/>
+        <f>COUNTIF(J12:J21,"&lt;"&amp;DATE(2026,5,4))</f>
       </c>
     </row>
     <row r="30"/>
@@ -1323,7 +1301,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="34" customHeight="1">
+    <row r="41" ht="50.5" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Information Security Analyst</t>
@@ -1378,7 +1356,7 @@
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1">
+    <row r="45" ht="50.5" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1404,11 +1382,11 @@
       <c r="G45" s="12" t="n"/>
     </row>
     <row r="46"/>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="2" t="n"/>
+    <row r="47">
+      <c r="A47"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:G6"/>
@@ -1436,18 +1414,11 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A47:G47"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E12:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
-      <formula1>"Active,Under Review,Retired,Decommissioned"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>